--- a/backend/data/ci_s4_overbooking_mixed.xlsx
+++ b/backend/data/ci_s4_overbooking_mixed.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Commercial Invoice" sheetId="1" r:id="rId1"/>
+    <sheet name="CI" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G24"/>
+  <cols>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,7 +436,7 @@
         <v>Invoice No:</v>
       </c>
       <c r="B2" t="str">
-        <v>CI-S4-OVERBOOK-001</v>
+        <v>CI-004-OVERBOOK-MIX</v>
       </c>
       <c r="C2" t="str">
         <v>Invoice Date:</v>
@@ -470,19 +479,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PO-FW26-001</v>
+        <v>PO-FW26-004</v>
       </c>
       <c r="B4">
-        <v>9000</v>
+        <v>6480</v>
       </c>
       <c r="C4">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="D4">
-        <v>1800</v>
+        <v>5184</v>
       </c>
       <c r="E4">
-        <v>22.5</v>
+        <v>77.8</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -617,7 +626,7 @@
         <v>Qty</v>
       </c>
       <c r="D10" t="str">
-        <v>Unit Price (USD)</v>
+        <v>Unit $</v>
       </c>
       <c r="E10" t="str">
         <v>Total Price (USD)</v>
@@ -631,145 +640,329 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>TEN7101-FGN-XS</v>
+        <v>TEN7401-BLK-XS</v>
       </c>
       <c r="B11" t="str">
-        <v>FW26 Fleece Jacket - Forest Green XS</v>
+        <v>Down Puffer Jacket Black</v>
       </c>
       <c r="C11">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="D11">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="E11">
-        <v>13200</v>
+        <v>8400</v>
       </c>
       <c r="F11">
         <v>160</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TEN7101-FGN-S</v>
+        <v>TEN7401-BLK-S</v>
       </c>
       <c r="B12" t="str">
-        <v>FW26 Fleece Jacket - Forest Green S</v>
+        <v>Down Puffer Jacket Black</v>
       </c>
       <c r="C12">
-        <v>2000</v>
+        <v>650</v>
       </c>
       <c r="D12">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="E12">
-        <v>33000</v>
+        <v>27300</v>
       </c>
       <c r="F12">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TEN7101-FGN-M</v>
+        <v>TEN7401-BLK-M</v>
       </c>
       <c r="B13" t="str">
-        <v>FW26 Fleece Jacket - Forest Green M</v>
+        <v>Down Puffer Jacket Black</v>
       </c>
       <c r="C13">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="D13">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="E13">
-        <v>66000</v>
+        <v>42000</v>
       </c>
       <c r="F13">
         <v>800</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>TEN7101-FGN-GHOST</v>
+        <v>TEN7401-BLK-L</v>
       </c>
       <c r="B14" t="str">
-        <v>FW26 Fleece Jacket - Forest Green GHOST</v>
+        <v>Down Puffer Jacket Black</v>
       </c>
       <c r="C14">
-        <v>2200</v>
+        <v>800</v>
       </c>
       <c r="D14">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="E14">
-        <v>36300</v>
+        <v>33600</v>
       </c>
       <c r="F14">
-        <v>440</v>
+        <v>640</v>
       </c>
       <c r="G14">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>TEN7401-BLK-XL</v>
       </c>
       <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
+        <v>Down Puffer Jacket Black</v>
+      </c>
+      <c r="C15">
+        <v>350</v>
+      </c>
+      <c r="D15">
+        <v>42</v>
+      </c>
+      <c r="E15">
+        <v>14700</v>
+      </c>
+      <c r="F15">
+        <v>280</v>
+      </c>
+      <c r="G15">
+        <v>4.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>TEN7401-BLK-2X</v>
       </c>
       <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16" t="str">
-        <v/>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
+        <v>Down Puffer Jacket Black</v>
+      </c>
+      <c r="C16">
+        <v>200</v>
+      </c>
+      <c r="D16">
+        <v>42</v>
+      </c>
+      <c r="E16">
+        <v>8400</v>
+      </c>
+      <c r="F16">
+        <v>160</v>
+      </c>
+      <c r="G16">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TEN7401-MSG-XS</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Down Puffer Jacket Moss Green</v>
+      </c>
+      <c r="C17">
+        <v>280</v>
+      </c>
+      <c r="D17">
+        <v>42</v>
+      </c>
+      <c r="E17">
+        <v>11760</v>
+      </c>
+      <c r="F17">
+        <v>224</v>
+      </c>
+      <c r="G17">
+        <v>3.36</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TEN7401-MSG-S</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Down Puffer Jacket Moss Green</v>
+      </c>
+      <c r="C18">
+        <v>500</v>
+      </c>
+      <c r="D18">
+        <v>42</v>
+      </c>
+      <c r="E18">
+        <v>21000</v>
+      </c>
+      <c r="F18">
+        <v>400</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TEN7401-MSG-M</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Down Puffer Jacket Moss Green</v>
+      </c>
+      <c r="C19">
+        <v>1000</v>
+      </c>
+      <c r="D19">
+        <v>42</v>
+      </c>
+      <c r="E19">
+        <v>42000</v>
+      </c>
+      <c r="F19">
+        <v>800</v>
+      </c>
+      <c r="G19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TEN7401-MSG-L</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Down Puffer Jacket Moss Green</v>
+      </c>
+      <c r="C20">
+        <v>750</v>
+      </c>
+      <c r="D20">
+        <v>42</v>
+      </c>
+      <c r="E20">
+        <v>31500</v>
+      </c>
+      <c r="F20">
+        <v>600</v>
+      </c>
+      <c r="G20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TEN7401-MSG-XL</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Down Puffer Jacket Moss Green</v>
+      </c>
+      <c r="C21">
+        <v>500</v>
+      </c>
+      <c r="D21">
+        <v>42</v>
+      </c>
+      <c r="E21">
+        <v>21000</v>
+      </c>
+      <c r="F21">
+        <v>400</v>
+      </c>
+      <c r="G21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TEN7401-MSG-2X</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Down Puffer Jacket Moss Green</v>
+      </c>
+      <c r="C22">
+        <v>200</v>
+      </c>
+      <c r="D22">
+        <v>42</v>
+      </c>
+      <c r="E22">
+        <v>8400</v>
+      </c>
+      <c r="F22">
+        <v>160</v>
+      </c>
+      <c r="G22">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TEN7401-BLK-SAMPLE</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Down Puffer Jacket Black Sample</v>
+      </c>
+      <c r="C23">
+        <v>50</v>
+      </c>
+      <c r="D23">
+        <v>42</v>
+      </c>
+      <c r="E23">
+        <v>2100</v>
+      </c>
+      <c r="F23">
+        <v>40</v>
+      </c>
+      <c r="G23">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G24"/>
   </ignoredErrors>
 </worksheet>
 </file>